--- a/dataset_t6_grouped/results2/G3/G3_T2485_W0065F0003T0006Z000C1N6_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T2485_W0065F0003T0006Z000C1N6_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>73.01561739033637</v>
+        <v>11.86503782592966</v>
       </c>
       <c r="D2" t="n">
-        <v>73.66758288260425</v>
+        <v>11.97098221842319</v>
       </c>
       <c r="E2" t="n">
-        <v>1.131247692111749</v>
+        <v>0.1838277499681586</v>
       </c>
       <c r="F2" t="n">
-        <v>1.117838978575698</v>
+        <v>0.1816488340185503</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>75.27811277455987</v>
+        <v>12.23269332586598</v>
       </c>
       <c r="D3" t="n">
-        <v>75.90326083975565</v>
+        <v>12.33427988646029</v>
       </c>
       <c r="E3" t="n">
-        <v>1.131247692111749</v>
+        <v>0.1838277499681586</v>
       </c>
       <c r="F3" t="n">
-        <v>1.117838978575698</v>
+        <v>0.1816488340185503</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
